--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5684,7 +5684,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>178</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5989,7 +5989,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>187</v>
       </c>
@@ -6004,13 +6004,13 @@
         <v>62</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -6092,7 +6092,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>190</v>
       </c>
@@ -6107,13 +6107,13 @@
         <v>191</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -6401,7 +6401,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>202</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$142</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4440" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4470" uniqueCount="492">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -847,6 +847,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Encounter.statusCode</t>
@@ -1263,6 +1267,15 @@
   </si>
   <si>
     <t>ParticipantRole.code</t>
+  </si>
+  <si>
+    <t>Encounter.participant:lieuExecution.participantRole.sdtcSpecialty</t>
+  </si>
+  <si>
+    <t>Encounter.participant.participantRole.sdtcSpecialty</t>
+  </si>
+  <si>
+    <t>ParticipantRole.sdtcSpecialty</t>
   </si>
   <si>
     <t>Encounter.participant:lieuExecution.participantRole.addr</t>
@@ -1844,7 +1857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK141"/>
+  <dimension ref="A1:AK142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="77.77734375" customWidth="true" bestFit="true"/>
@@ -8132,7 +8145,7 @@
         <v>74</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>74</v>
+        <v>271</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>74</v>
@@ -8140,10 +8153,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8199,25 +8212,25 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8237,10 +8250,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8263,13 +8276,13 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8320,7 +8333,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8340,10 +8353,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8366,7 +8379,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -8419,7 +8432,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8439,10 +8452,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8465,13 +8478,13 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8502,7 +8515,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8520,7 +8533,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8540,10 +8553,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8566,7 +8579,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8619,7 +8632,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8639,10 +8652,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8665,7 +8678,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8718,7 +8731,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8738,10 +8751,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8764,13 +8777,13 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8821,7 +8834,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8841,10 +8854,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8942,10 +8955,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9043,10 +9056,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9144,10 +9157,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9245,10 +9258,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9348,10 +9361,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9451,10 +9464,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9554,10 +9567,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9657,10 +9670,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9758,10 +9771,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9795,7 +9808,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>74</v>
@@ -9817,7 +9830,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9835,7 +9848,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9855,10 +9868,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9881,7 +9894,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9934,7 +9947,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9954,10 +9967,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9980,13 +9993,13 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10037,7 +10050,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -10057,10 +10070,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10083,7 +10096,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -10136,7 +10149,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10156,10 +10169,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10182,7 +10195,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -10235,7 +10248,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
@@ -10255,10 +10268,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10281,13 +10294,13 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10338,7 +10351,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10358,10 +10371,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10384,13 +10397,13 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10441,7 +10454,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10461,10 +10474,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10487,7 +10500,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10528,7 +10541,7 @@
         <v>74</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AC85" s="2"/>
       <c r="AD85" t="s" s="2">
@@ -10538,7 +10551,7 @@
         <v>125</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10558,13 +10571,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>74</v>
@@ -10586,13 +10599,13 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10643,7 +10656,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10663,10 +10676,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10764,10 +10777,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10865,10 +10878,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10966,10 +10979,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11067,10 +11080,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11170,10 +11183,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11273,10 +11286,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11376,10 +11389,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11479,10 +11492,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11580,10 +11593,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11620,7 +11633,7 @@
         <v>74</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>74</v>
@@ -11639,7 +11652,7 @@
       </c>
       <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>74</v>
@@ -11657,7 +11670,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
@@ -11677,10 +11690,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11714,7 +11727,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>74</v>
@@ -11736,7 +11749,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>74</v>
@@ -11754,7 +11767,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11774,10 +11787,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11800,7 +11813,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -11853,7 +11866,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11873,10 +11886,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11899,7 +11912,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11952,7 +11965,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11972,10 +11985,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11998,7 +12011,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -12051,7 +12064,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -12071,10 +12084,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12097,7 +12110,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -12150,7 +12163,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -12170,10 +12183,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12271,10 +12284,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12372,10 +12385,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12473,10 +12486,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12574,10 +12587,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12677,10 +12690,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12780,10 +12793,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12883,10 +12896,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12986,10 +12999,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13087,10 +13100,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13120,14 +13133,14 @@
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>74</v>
@@ -13146,7 +13159,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>74</v>
@@ -13164,7 +13177,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13184,10 +13197,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13213,10 +13226,10 @@
         <v>95</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -13267,7 +13280,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13287,10 +13300,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13313,7 +13326,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13366,7 +13379,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13386,10 +13399,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13412,7 +13425,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13445,7 +13458,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>74</v>
@@ -13463,7 +13476,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13481,12 +13494,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13500,7 +13513,7 @@
         <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>74</v>
@@ -13509,14 +13522,10 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="L115" s="2"/>
+      <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13566,7 +13575,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13586,10 +13595,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13612,7 +13621,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>264</v>
+        <v>410</v>
       </c>
       <c r="L116" t="s" s="2">
         <v>411</v>
@@ -13687,7 +13696,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
         <v>413</v>
       </c>
@@ -13703,10 +13712,10 @@
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>74</v>
@@ -13715,10 +13724,14 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L117" s="2"/>
-      <c r="M117" s="2"/>
+      <c r="M117" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -13774,7 +13787,7 @@
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>74</v>
@@ -13786,7 +13799,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
         <v>417</v>
       </c>
@@ -13805,7 +13818,7 @@
         <v>75</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>74</v>
@@ -13885,7 +13898,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
         <v>421</v>
       </c>
@@ -13896,9 +13909,7 @@
       <c r="D119" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E119" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
@@ -13906,7 +13917,7 @@
         <v>75</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>74</v>
@@ -13915,12 +13926,10 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="L119" s="2"/>
-      <c r="M119" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -13946,11 +13955,13 @@
         <v>74</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y119" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z119" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>74</v>
@@ -13968,7 +13979,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>89</v>
+        <v>424</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13988,21 +13999,23 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E120" s="2"/>
+      <c r="E120" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>74</v>
@@ -14014,11 +14027,11 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14045,13 +14058,11 @@
         <v>74</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>74</v>
@@ -14069,13 +14080,13 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>74</v>
@@ -14089,10 +14100,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14103,7 +14114,7 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>74</v>
@@ -14115,11 +14126,11 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -14170,19 +14181,19 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>74</v>
@@ -14190,18 +14201,16 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E122" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
@@ -14218,11 +14227,11 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -14249,11 +14258,13 @@
         <v>74</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y122" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z122" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>74</v>
@@ -14271,7 +14282,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14283,7 +14294,7 @@
         <v>74</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>74</v>
@@ -14291,17 +14302,17 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F123" t="s" s="2">
         <v>80</v>
@@ -14319,11 +14330,11 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14350,13 +14361,11 @@
         <v>74</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>74</v>
@@ -14374,7 +14383,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14394,17 +14403,17 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F124" t="s" s="2">
         <v>80</v>
@@ -14422,11 +14431,11 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14477,7 +14486,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14497,20 +14506,20 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F125" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
         <v>75</v>
@@ -14525,11 +14534,11 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -14538,7 +14547,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>74</v>
@@ -14580,7 +14589,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14600,17 +14609,17 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F126" t="s" s="2">
         <v>75</v>
@@ -14628,11 +14637,11 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14641,7 +14650,7 @@
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>74</v>
@@ -14683,7 +14692,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14703,21 +14712,23 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E127" s="2"/>
+      <c r="E127" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F127" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>74</v>
@@ -14729,11 +14740,11 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14784,13 +14795,13 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>74</v>
@@ -14804,10 +14815,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14818,7 +14829,7 @@
         <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>74</v>
@@ -14830,21 +14841,23 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
+      <c r="M128" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
-        <v>441</v>
+        <v>74</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>442</v>
+        <v>74</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>74</v>
@@ -14859,11 +14872,13 @@
         <v>74</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y128" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z128" t="s" s="2">
-        <v>443</v>
+        <v>74</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>74</v>
@@ -14881,13 +14896,13 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>444</v>
+        <v>126</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>74</v>
@@ -14901,10 +14916,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14934,14 +14949,14 @@
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
-        <v>74</v>
+        <v>445</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>447</v>
+        <v>74</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>74</v>
+        <v>446</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>74</v>
@@ -14960,25 +14975,25 @@
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14998,10 +15013,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15024,7 +15039,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>278</v>
+        <v>85</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15035,7 +15050,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>74</v>
+        <v>451</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>74</v>
@@ -15053,7 +15068,7 @@
         <v>74</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>184</v>
+        <v>87</v>
       </c>
       <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
@@ -15109,7 +15124,7 @@
         <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>74</v>
@@ -15121,7 +15136,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>456</v>
+        <v>279</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -15150,13 +15165,11 @@
         <v>74</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>74</v>
+        <v>456</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>74</v>
@@ -15180,7 +15193,7 @@
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>74</v>
@@ -15192,7 +15205,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
         <v>458</v>
       </c>
@@ -15205,13 +15218,13 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>74</v>
@@ -15222,12 +15235,8 @@
       <c r="K132" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L132" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="L132" s="2"/>
+      <c r="M132" s="2"/>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -15277,7 +15286,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15295,12 +15304,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B133" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15308,13 +15317,13 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>74</v>
@@ -15323,11 +15332,13 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15378,13 +15389,13 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>74</v>
@@ -15398,10 +15409,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B134" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15424,10 +15435,12 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>215</v>
+        <v>469</v>
       </c>
       <c r="L134" s="2"/>
-      <c r="M134" s="2"/>
+      <c r="M134" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -15477,7 +15490,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15497,10 +15510,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15523,7 +15536,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>473</v>
+        <v>215</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15594,16 +15607,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
         <v>475</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C136" t="s" s="2">
         <v>476</v>
       </c>
+      <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>74</v>
       </c>
@@ -15612,10 +15623,10 @@
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>74</v>
@@ -15677,13 +15688,13 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>321</v>
+        <v>478</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>74</v>
@@ -15695,14 +15706,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C137" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="D137" t="s" s="2">
         <v>74</v>
       </c>
@@ -15714,7 +15727,7 @@
         <v>81</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>74</v>
@@ -15723,7 +15736,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15776,7 +15789,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>478</v>
+        <v>322</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15796,10 +15809,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15822,7 +15835,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15875,7 +15888,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15895,10 +15908,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15921,7 +15934,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -15974,7 +15987,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -15994,10 +16007,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16020,7 +16033,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16073,7 +16086,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -16093,10 +16106,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16119,7 +16132,7 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16172,7 +16185,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -16190,8 +16203,107 @@
         <v>74</v>
       </c>
     </row>
+    <row r="142" hidden="true">
+      <c r="A142" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L142" s="2"/>
+      <c r="M142" s="2"/>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK141">
+  <autoFilter ref="A1:AK142">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16201,7 +16313,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI140">
+  <conditionalFormatting sqref="A2:AI141">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
